--- a/vse-loti/340511474/spec-340511474.xlsx
+++ b/vse-loti/340511474/spec-340511474.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Трубы стальные бесшовные с тепловой изоляцией из пенополиуретана в оцинкованной оболочке, наружный диаметр 76 мм, стенка 3,5 мм, оболочка 160 мм (ФСБЦ-23.4.01.03-0152; смета поз. 3)</t>
+          <t>Трубы стальные бесшовные с тепловой изоляцией из пенополиуретана в оцинкованной оболочке, наружный диаметр 76 мм, толщина стенки 3,5 мм, наружный диаметр оболочки 160 мм (ФСБЦ-23.4.01.03-0152; смета поз. 3)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Отвод стальной 90° с тепловой изоляцией ППУ в оцинкованной оболочке, D трубы 76 мм, D изоляции 160 мм, плечо 1000 мм (ФСБЦ-23.8.02.02-0058; смета поз. 5)</t>
+          <t>Отвод стальной 90° с тепловой изоляцией из пенополиуретана в оцинкованной оболочке, наружный диаметр стальной трубы 76 мм, наружный диаметр изоляции 160 мм, длина плеча 1000 мм (ФСБЦ-23.8.02.02-0058; смета поз. 5)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Комплект для изоляции сварного стыка стальных труб ППУ в оцинкованной оболочке, D трубы 76 мм, D изоляции 160 мм (ФСБЦ-24.1.01.06-1352; смета поз. 7)</t>
+          <t>Комплект для изоляции сварного стыка стальных труб с теплоизоляцией из пенополиуретана в оцинкованной оболочке, наружный диаметр трубы 76 мм, наружный диаметр изоляции 160 мм (ФСБЦ-24.1.01.06-1352; смета поз. 7)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -652,19 +652,18 @@
         <v>4663628.51</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Источник: НМЦД.xlsx (лист «Капитальный ремонт ГВС от котельной №23», текущий уровень цен, без НДС)
-ТЗ Модернизация ГВС д. Крюково.docx (п. 8: Д 76 мм, L = 630 м)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Источник: НМЦД.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="10"/>
+    <row r="11"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:B10"/>
+    <mergeCell ref="A9:B11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
